--- a/src/main/resources/python/MultifacetedModeling/Results/OnTrain/KnowledgeKernel/GPR/0.xlsx
+++ b/src/main/resources/python/MultifacetedModeling/Results/OnTrain/KnowledgeKernel/GPR/0.xlsx
@@ -442,56 +442,56 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1.083984375</t>
+          <t>1.298828125</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1.474609375</t>
+          <t>1.103515625</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1.298828125</t>
+          <t>1.474609375</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1.083984375</t>
+          <t>1.044921875</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0.673828125</t>
+          <t>1.11328125</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1.376953125</t>
+          <t>1.474609375</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0.91796875</t>
+          <t>1.46484375</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1.044921875</t>
+          <t>1.220703125</t>
         </is>
       </c>
     </row>
@@ -505,91 +505,91 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1.474609375</t>
+          <t>0.78125</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0.908203125</t>
+          <t>1.455078125</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1.50390625</t>
+          <t>1.171875</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1.005859375</t>
+          <t>0.64453125</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0.791015625</t>
+          <t>1.484375</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1.34765625</t>
+          <t>0.830078125</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1.15234375</t>
+          <t>1.328125</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1.357421875</t>
+          <t>0.908203125</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1.23046875</t>
+          <t>0.869140625</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1.259765625</t>
+          <t>1.044921875</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1.474609375</t>
+          <t>1.298828125</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0.64453125</t>
+          <t>1.240234375</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1.2109375</t>
+          <t>0.68359375</t>
         </is>
       </c>
     </row>
@@ -617,154 +617,154 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.3260569565619278</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1.4742408147963033</t>
+          <t>1.3788016250018416</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.4951861059439011</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.9898230132305343</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0.9047032159873538</t>
+          <t>1.0880068549095938</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1.1385313451659727</t>
+          <t>1.4581984078723735</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1.1385313451659727</t>
+          <t>1.456596563343254</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1.1385313451659727</t>
+          <t>1.2579176729523738</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1.1385313451659727</t>
+          <t>0.9164245210968431</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1.4742408147963033</t>
+          <t>0.8536841372134631</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1.1385313451659727</t>
+          <t>1.444394775309263</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1.1385313451659727</t>
+          <t>1.4263859913265549</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1.1385313451659727</t>
+          <t>0.4945120480122682</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1.1385313451659727</t>
+          <t>1.474449462509284</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1.1385313451659727</t>
+          <t>0.20408632870574195</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1.1385313451659727</t>
+          <t>1.1498170285982496</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1.1385313451659727</t>
+          <t>0.36190528708524994</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1.1385313451659727</t>
+          <t>0.9473117439812597</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1.2786575462268814</t>
+          <t>1.0265133925717578</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1.4494705772113932</t>
+          <t>1.3192510229449397</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0.9047032159873538</t>
+          <t>1.1672166103003576</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.6645590261034329</t>
         </is>
       </c>
     </row>
@@ -802,17 +802,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0.37211577830470477</t>
+          <t>0.07083468130087107</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.529582037455366</t>
+          <t>0.21282562013153145</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.4559901621478346</t>
+          <t>0.32730788396828336</t>
         </is>
       </c>
     </row>
